--- a/examples/excel_input/example_iso_CLI.xlsx
+++ b/examples/excel_input/example_iso_CLI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haleyaldrich-my.sharepoint.com/personal/schase_haleyaldrich_com/Documents/Documents/git-projects/geofig-engine/examples/excel_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="11_2CB7ACC5603773FFFF69D4D2005155B5B0B50DA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{415E35F8-3885-4331-85E7-44C4227BD2CA}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="11_2CB7ACC5603773FFFF69D4D2005155B5B0B50DA8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{145FC34C-AE81-49D4-AC99-46AB8204A918}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="116">
   <si>
     <t>Delta Oxygen 18 in Sulfate</t>
   </si>
@@ -380,7 +380,10 @@
     <t>sulfate</t>
   </si>
   <si>
-    <t>water</t>
+    <t>O18</t>
+  </si>
+  <si>
+    <t>Deut</t>
   </si>
 </sst>
 </file>
@@ -911,13 +914,13 @@
         <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>114</v>
@@ -2432,17 +2435,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d9348919-c7aa-4960-8da4-a5e70343baa0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f01f682a-c7fc-4c44-a5b2-c6a14a23e87f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6D33989EE13B49A44C88397179B40B" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c4d9c804372d0512bef34db885c699a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d9348919-c7aa-4960-8da4-a5e70343baa0" xmlns:ns3="f01f682a-c7fc-4c44-a5b2-c6a14a23e87f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c53ec3766401f5c25f1c03937ca325c" ns2:_="" ns3:_="">
     <xsd:import namespace="d9348919-c7aa-4960-8da4-a5e70343baa0"/>
@@ -2691,6 +2683,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d9348919-c7aa-4960-8da4-a5e70343baa0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f01f682a-c7fc-4c44-a5b2-c6a14a23e87f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2701,17 +2704,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86C412A8-43FB-4F0E-A212-6C8E1B6454CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d9348919-c7aa-4960-8da4-a5e70343baa0"/>
-    <ds:schemaRef ds:uri="f01f682a-c7fc-4c44-a5b2-c6a14a23e87f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9157C922-C7A4-40E8-B194-22DA1F393C0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2730,6 +2722,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86C412A8-43FB-4F0E-A212-6C8E1B6454CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d9348919-c7aa-4960-8da4-a5e70343baa0"/>
+    <ds:schemaRef ds:uri="f01f682a-c7fc-4c44-a5b2-c6a14a23e87f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A347A27-4155-49D9-8501-B7EBED70DB04}">
   <ds:schemaRefs>
